--- a/samples/Tax_Rate_Check_FIXED.xlsx
+++ b/samples/Tax_Rate_Check_FIXED.xlsx
@@ -19,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="000"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Arial"/>
@@ -72,13 +74,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
@@ -590,21 +593,6 @@
           <t>NE City Code</t>
         </is>
       </c>
-      <c r="U4" s="5" t="inlineStr">
-        <is>
-          <t>Match Row #</t>
-        </is>
-      </c>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
-          <t>Match Flag</t>
-        </is>
-      </c>
-      <c r="W4" s="5" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -667,21 +655,8 @@
       <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T5" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" hidden="1" s="4">
@@ -726,6 +701,7 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
+      <c r="T6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -788,21 +764,8 @@
       <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T7" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8" hidden="1" s="4">
@@ -840,6 +803,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
+      <c r="T8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -902,21 +866,8 @@
       <c r="S9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T9" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -983,11 +934,7 @@
       <c r="S10" t="n">
         <v>0</v>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>OOS</t>
-        </is>
-      </c>
+      <c r="T10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1050,21 +997,8 @@
       <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T11" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1128,11 +1062,7 @@
       <c r="S12" t="n">
         <v>0</v>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>OOS</t>
-        </is>
-      </c>
+      <c r="T12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1195,23 +1125,8 @@
       <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>FALLBACK - row 97027 (unvalidated)</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>FALLBACK</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T13" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1275,21 +1190,8 @@
       <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>10639</v>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T14" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1353,21 +1255,8 @@
       <c r="S15" t="n">
         <v>0</v>
       </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T15" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1431,21 +1320,8 @@
       <c r="S16" t="n">
         <v>0</v>
       </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>198355</v>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T16" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1509,21 +1385,8 @@
       <c r="S17" t="n">
         <v>0</v>
       </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>198355</v>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T17" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1587,21 +1450,8 @@
       <c r="S18" t="n">
         <v>0</v>
       </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>198355</v>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T18" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1665,21 +1515,8 @@
       <c r="S19" t="n">
         <v>0</v>
       </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>198355</v>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T19" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1743,21 +1580,8 @@
       <c r="S20" t="n">
         <v>0</v>
       </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>190253</v>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T20" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1821,23 +1645,8 @@
       <c r="S21" t="n">
         <v>0</v>
       </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>FALLBACK - row 33986 (unvalidated)</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>FALLBACK</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T21" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1897,23 +1706,8 @@
       <c r="S22" t="n">
         <v>0</v>
       </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>FALLBACK - row 170755 (unvalidated)</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>FALLBACK</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T22" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1977,23 +1771,8 @@
       <c r="S23" t="n">
         <v>0</v>
       </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>FALLBACK - row 170755 (unvalidated)</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>FALLBACK</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T23" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2057,16 +1836,7 @@
       <c r="S24" t="n">
         <v>0</v>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
-      </c>
+      <c r="T24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2129,16 +1899,7 @@
       <c r="S25" t="n">
         <v>0</v>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
-      </c>
+      <c r="T25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2201,23 +1962,8 @@
       <c r="S26" t="n">
         <v>0</v>
       </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>FALLBACK - row 170755 (unvalidated)</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>FALLBACK</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T26" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2281,21 +2027,8 @@
       <c r="S27" t="n">
         <v>0</v>
       </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>260881</v>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T27" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2359,21 +2092,8 @@
       <c r="S28" t="n">
         <v>0</v>
       </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T28" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2463,21 +2183,8 @@
           <t>170</t>
         </is>
       </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>205510</v>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T29" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2541,21 +2248,8 @@
       <c r="S30" t="n">
         <v>0</v>
       </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>260881</v>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T30" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2631,21 +2325,8 @@
           <t>084</t>
         </is>
       </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>120272</v>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T31" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2709,16 +2390,7 @@
       <c r="S32" t="n">
         <v>0</v>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
-      </c>
+      <c r="T32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2781,21 +2453,8 @@
       <c r="S33" t="n">
         <v>0</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T33" s="6" t="n">
         <v>170</v>
-      </c>
-      <c r="U33" t="n">
-        <v>240732</v>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
       </c>
     </row>
     <row r="34">
@@ -2859,16 +2518,7 @@
       <c r="S34" t="n">
         <v>0</v>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
-      </c>
+      <c r="T34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2957,21 +2607,8 @@
           <t>094</t>
         </is>
       </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>237887</v>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T35" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3061,16 +2698,7 @@
           <t>094</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>NO CODE-CITY</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
-      </c>
+      <c r="T36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3159,16 +2787,7 @@
           <t>104</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>NO CODE-CITY</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
-      </c>
+      <c r="T37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3257,16 +2876,7 @@
           <t>104</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>NO CODE-CITY</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
-      </c>
+      <c r="T38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3355,21 +2965,8 @@
           <t>104</t>
         </is>
       </c>
-      <c r="T39" t="n">
+      <c r="T39" s="6" t="n">
         <v>94</v>
-      </c>
-      <c r="U39" t="n">
-        <v>24820</v>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
       </c>
     </row>
     <row r="40">
@@ -3433,21 +3030,8 @@
       <c r="S40" t="n">
         <v>0</v>
       </c>
-      <c r="T40" t="n">
+      <c r="T40" s="6" t="n">
         <v>94</v>
-      </c>
-      <c r="U40" t="n">
-        <v>121611</v>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
       </c>
     </row>
     <row r="41">
@@ -3511,21 +3095,8 @@
       <c r="S41" t="n">
         <v>0</v>
       </c>
-      <c r="T41" t="n">
+      <c r="T41" s="6" t="n">
         <v>104</v>
-      </c>
-      <c r="U41" t="n">
-        <v>156202</v>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
       </c>
     </row>
     <row r="42">
@@ -3589,21 +3160,8 @@
       <c r="S42" t="n">
         <v>0</v>
       </c>
-      <c r="T42" t="n">
+      <c r="T42" s="6" t="n">
         <v>104</v>
-      </c>
-      <c r="U42" t="n">
-        <v>156202</v>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
       </c>
     </row>
     <row r="43">
@@ -3667,21 +3225,8 @@
       <c r="S43" t="n">
         <v>0</v>
       </c>
-      <c r="T43" t="n">
+      <c r="T43" s="6" t="n">
         <v>104</v>
-      </c>
-      <c r="U43" t="n">
-        <v>156202</v>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
       </c>
     </row>
     <row r="44">
@@ -3745,21 +3290,8 @@
       <c r="S44" t="n">
         <v>0</v>
       </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>40482</v>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T44" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -3823,21 +3355,8 @@
       <c r="S45" t="n">
         <v>0</v>
       </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>177013</v>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T45" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3901,21 +3420,8 @@
       <c r="S46" t="n">
         <v>0</v>
       </c>
-      <c r="T46" t="n">
+      <c r="T46" s="6" t="n">
         <v>134</v>
-      </c>
-      <c r="U46" t="n">
-        <v>145588</v>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>OK - REPAIRED: direction on the wrong end</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
       </c>
     </row>
     <row r="47">
@@ -4005,21 +3511,8 @@
           <t>179</t>
         </is>
       </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>269255</v>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T47" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4109,21 +3602,8 @@
           <t>198</t>
         </is>
       </c>
-      <c r="T48" t="n">
+      <c r="T48" s="6" t="n">
         <v>134</v>
-      </c>
-      <c r="U48" t="n">
-        <v>208594</v>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>OK - REPAIRED: direction on the wrong end</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
       </c>
     </row>
     <row r="49">
@@ -4161,23 +3641,8 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>FALLBACK - row 114521 (unvalidated)</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>FALLBACK</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T49" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4259,16 +3724,7 @@
           <t>210</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
-      </c>
+      <c r="T50" s="6" t="n"/>
     </row>
     <row r="51" hidden="1" s="4">
       <c r="A51" t="n">
@@ -4305,6 +3761,7 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
+      <c r="T51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4367,21 +3824,8 @@
       <c r="S52" t="n">
         <v>0</v>
       </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T52" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4445,21 +3889,8 @@
       <c r="S53" t="n">
         <v>0</v>
       </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T53" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4523,21 +3954,8 @@
       <c r="S54" t="n">
         <v>0</v>
       </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T54" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -4619,21 +4037,8 @@
           <t>210</t>
         </is>
       </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T55" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -4697,21 +4102,8 @@
       <c r="S56" t="n">
         <v>0</v>
       </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T56" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -4775,21 +4167,8 @@
       <c r="S57" t="n">
         <v>0</v>
       </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T57" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -4853,21 +4232,8 @@
       <c r="S58" t="n">
         <v>0</v>
       </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T58" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4931,21 +4297,8 @@
       <c r="S59" t="n">
         <v>0</v>
       </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T59" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5035,21 +4388,8 @@
           <t>229</t>
         </is>
       </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T60" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5113,21 +4453,8 @@
       <c r="S61" t="n">
         <v>0</v>
       </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T61" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -5191,21 +4518,8 @@
       <c r="S62" t="n">
         <v>0</v>
       </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T62" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -5269,21 +4583,8 @@
       <c r="S63" t="n">
         <v>0</v>
       </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T63" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -5347,21 +4648,8 @@
       <c r="S64" t="n">
         <v>0</v>
       </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T64" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5425,21 +4713,8 @@
       <c r="S65" t="n">
         <v>0</v>
       </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T65" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -5503,21 +4778,8 @@
       <c r="S66" t="n">
         <v>0</v>
       </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T66" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5605,21 +4867,8 @@
           <t>201</t>
         </is>
       </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T67" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -5683,21 +4932,8 @@
       <c r="S68" t="n">
         <v>0</v>
       </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T68" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -5761,21 +4997,8 @@
       <c r="S69" t="n">
         <v>0</v>
       </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T69" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -5863,21 +5086,8 @@
           <t>285</t>
         </is>
       </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T70" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -5967,21 +5177,8 @@
           <t>305</t>
         </is>
       </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T71" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -6045,21 +5242,8 @@
       <c r="S72" t="n">
         <v>0</v>
       </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T72" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -6149,21 +5333,8 @@
           <t>190</t>
         </is>
       </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T73" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -6227,21 +5398,8 @@
       <c r="S74" t="n">
         <v>0</v>
       </c>
-      <c r="T74" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T74" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -6305,21 +5463,8 @@
       <c r="S75" t="n">
         <v>0</v>
       </c>
-      <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T75" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6383,21 +5528,8 @@
       <c r="S76" t="n">
         <v>0</v>
       </c>
-      <c r="T76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T76" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -6461,21 +5593,8 @@
       <c r="S77" t="n">
         <v>0</v>
       </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T77" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78" hidden="1" s="4">
@@ -6513,6 +5632,7 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
+      <c r="T78" s="6" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6601,21 +5721,8 @@
           <t>269</t>
         </is>
       </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T79" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -6679,11 +5786,7 @@
       <c r="S80" t="n">
         <v>0</v>
       </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>OOS</t>
-        </is>
-      </c>
+      <c r="T80" s="6" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6746,21 +5849,8 @@
       <c r="S81" t="n">
         <v>0</v>
       </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T81" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -6850,11 +5940,7 @@
           <t>454</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>OOS</t>
-        </is>
-      </c>
+      <c r="T82" s="6" t="n"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6943,23 +6029,8 @@
           <t>454</t>
         </is>
       </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>FALLBACK - row 97027 (unvalidated)</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>FALLBACK</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T83" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -7049,21 +6120,8 @@
           <t>454</t>
         </is>
       </c>
-      <c r="T84" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" t="n">
-        <v>10639</v>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T84" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -7151,21 +6209,8 @@
           <t>470</t>
         </is>
       </c>
-      <c r="T85" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T85" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -7253,21 +6298,8 @@
           <t>470</t>
         </is>
       </c>
-      <c r="T86" t="n">
-        <v>0</v>
-      </c>
-      <c r="U86" t="n">
-        <v>198355</v>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T86" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -7331,21 +6363,8 @@
       <c r="S87" t="n">
         <v>0</v>
       </c>
-      <c r="T87" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" t="n">
-        <v>198355</v>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T87" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -7409,21 +6428,8 @@
       <c r="S88" t="n">
         <v>0</v>
       </c>
-      <c r="T88" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" t="n">
-        <v>198355</v>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T88" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -7487,21 +6493,8 @@
       <c r="S89" t="n">
         <v>0</v>
       </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
-        <v>198355</v>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T89" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -7565,21 +6558,8 @@
       <c r="S90" t="n">
         <v>0</v>
       </c>
-      <c r="T90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="n">
-        <v>190253</v>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T90" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -7643,23 +6623,8 @@
       <c r="S91" t="n">
         <v>0</v>
       </c>
-      <c r="T91" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>FALLBACK - row 33986 (unvalidated)</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>FALLBACK</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T91" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -7723,23 +6688,8 @@
       <c r="S92" t="n">
         <v>0</v>
       </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>FALLBACK - row 170755 (unvalidated)</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>FALLBACK</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T92" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -7803,23 +6753,8 @@
       <c r="S93" t="n">
         <v>0</v>
       </c>
-      <c r="T93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>FALLBACK - row 170755 (unvalidated)</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>FALLBACK</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T93" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -7883,16 +6818,7 @@
       <c r="S94" t="n">
         <v>0</v>
       </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
-      </c>
+      <c r="T94" s="6" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -7955,16 +6881,7 @@
       <c r="S95" t="n">
         <v>0</v>
       </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
-      </c>
+      <c r="T95" s="6" t="n"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -8027,23 +6944,8 @@
       <c r="S96" t="n">
         <v>0</v>
       </c>
-      <c r="T96" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>FALLBACK - row 170755 (unvalidated)</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>FALLBACK</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T96" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -8107,21 +7009,8 @@
       <c r="S97" t="n">
         <v>0</v>
       </c>
-      <c r="T97" t="n">
-        <v>0</v>
-      </c>
-      <c r="U97" t="n">
-        <v>260881</v>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T97" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -8185,21 +7074,8 @@
       <c r="S98" t="n">
         <v>0</v>
       </c>
-      <c r="T98" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T98" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -8263,21 +7139,8 @@
       <c r="S99" t="n">
         <v>0</v>
       </c>
-      <c r="T99" t="n">
-        <v>0</v>
-      </c>
-      <c r="U99" t="n">
-        <v>205510</v>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T99" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -8341,21 +7204,8 @@
       <c r="S100" t="n">
         <v>0</v>
       </c>
-      <c r="T100" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" t="n">
-        <v>260881</v>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T100" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -8439,21 +7289,8 @@
           <t>351</t>
         </is>
       </c>
-      <c r="T101" t="n">
-        <v>0</v>
-      </c>
-      <c r="U101" t="n">
-        <v>120272</v>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T101" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -8517,16 +7354,7 @@
       <c r="S102" t="n">
         <v>0</v>
       </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
-      </c>
+      <c r="T102" s="6" t="n"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -8589,21 +7417,8 @@
       <c r="S103" t="n">
         <v>0</v>
       </c>
-      <c r="T103" t="n">
+      <c r="T103" s="6" t="n">
         <v>170</v>
-      </c>
-      <c r="U103" t="n">
-        <v>240732</v>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
       </c>
     </row>
     <row r="104" hidden="1" s="4">
@@ -8641,6 +7456,7 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr"/>
+      <c r="T104" s="6" t="n"/>
     </row>
     <row r="105" hidden="1" s="4">
       <c r="A105" t="n">
@@ -8677,6 +7493,7 @@
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr"/>
+      <c r="T105" s="6" t="n"/>
     </row>
     <row r="106" hidden="1" s="4">
       <c r="A106" t="n">
@@ -8713,6 +7530,7 @@
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr"/>
+      <c r="T106" s="6" t="n"/>
     </row>
     <row r="107" hidden="1" s="4">
       <c r="A107" t="n">
@@ -8749,6 +7567,7 @@
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr"/>
+      <c r="T107" s="6" t="n"/>
     </row>
     <row r="108" hidden="1" s="4">
       <c r="A108" t="n">
@@ -8785,6 +7604,7 @@
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr"/>
+      <c r="T108" s="6" t="n"/>
     </row>
     <row r="109" hidden="1" s="4">
       <c r="A109" t="n">
@@ -8821,6 +7641,7 @@
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr"/>
+      <c r="T109" s="6" t="n"/>
     </row>
     <row r="110" hidden="1" s="4">
       <c r="A110" t="n">
@@ -8857,6 +7678,7 @@
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr"/>
+      <c r="T110" s="6" t="n"/>
     </row>
     <row r="111" hidden="1" s="4">
       <c r="A111" t="n">
@@ -8893,6 +7715,7 @@
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr"/>
+      <c r="T111" s="6" t="n"/>
     </row>
     <row r="112" hidden="1" s="4">
       <c r="A112" t="n">
@@ -8929,6 +7752,7 @@
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr"/>
+      <c r="T112" s="6" t="n"/>
     </row>
     <row r="113" hidden="1" s="4">
       <c r="A113" t="n">
@@ -8965,6 +7789,7 @@
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr"/>
+      <c r="T113" s="6" t="n"/>
     </row>
     <row r="114" hidden="1" s="4">
       <c r="A114" t="n">
@@ -9001,6 +7826,7 @@
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr"/>
+      <c r="T114" s="6" t="n"/>
     </row>
     <row r="115" hidden="1" s="4">
       <c r="A115" t="n">
@@ -9037,6 +7863,7 @@
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr"/>
+      <c r="T115" s="6" t="n"/>
     </row>
     <row r="116" hidden="1" s="4">
       <c r="A116" t="n">
@@ -9073,6 +7900,7 @@
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr"/>
+      <c r="T116" s="6" t="n"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -9135,21 +7963,8 @@
       <c r="S117" t="n">
         <v>0</v>
       </c>
-      <c r="T117" t="n">
-        <v>0</v>
-      </c>
-      <c r="U117" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T117" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118" hidden="1" s="4">
@@ -9187,6 +8002,7 @@
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr"/>
+      <c r="T118" s="6" t="n"/>
     </row>
     <row r="119" hidden="1" s="4">
       <c r="A119" t="n">
@@ -9223,6 +8039,7 @@
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr"/>
+      <c r="T119" s="6" t="n"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -9285,21 +8102,8 @@
       <c r="S120" t="n">
         <v>0</v>
       </c>
-      <c r="T120" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" t="n">
-        <v>236652</v>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>2021 Q3 Address Data.xlsx</t>
-        </is>
+      <c r="T120" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11090,42 +9894,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>SheetRow</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Zip</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Engine City Code</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Engine Match Row #</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Engine Flag</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Source File</t>
         </is>
@@ -11148,7 +9952,7 @@
       <c r="D2" t="n">
         <v>68818</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
@@ -11182,7 +9986,7 @@
       <c r="D3" t="n">
         <v>68818</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
@@ -11216,7 +10020,7 @@
       <c r="D4" t="n">
         <v>68818</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
@@ -11250,7 +10054,7 @@
       <c r="D5" t="n">
         <v>68818</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
@@ -11284,7 +10088,7 @@
       <c r="D6" t="n">
         <v>68818</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -11320,7 +10124,7 @@
       <c r="D7" t="n">
         <v>68818</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
@@ -11354,7 +10158,7 @@
       <c r="D8" t="n">
         <v>68818</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
@@ -11388,7 +10192,7 @@
       <c r="D9" t="n">
         <v>68818</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
@@ -11422,7 +10226,7 @@
       <c r="D10" t="n">
         <v>68818</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
@@ -11456,7 +10260,7 @@
       <c r="D11" t="n">
         <v>68818</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
@@ -11490,7 +10294,7 @@
       <c r="D12" t="n">
         <v>68818</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
@@ -11524,7 +10328,7 @@
       <c r="D13" t="n">
         <v>68818</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
@@ -11558,7 +10362,7 @@
       <c r="D14" t="n">
         <v>68818</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
@@ -11594,7 +10398,7 @@
       <c r="D15" t="n">
         <v>68818</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
@@ -11630,7 +10434,7 @@
       <c r="D16" t="n">
         <v>68901</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
@@ -11666,6 +10470,7 @@
       <c r="D17" t="n">
         <v>68818</v>
       </c>
+      <c r="E17" s="6" t="n"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>NO MATCH</t>
@@ -11694,6 +10499,7 @@
       <c r="D18" t="n">
         <v>68818</v>
       </c>
+      <c r="E18" s="6" t="n"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>NO MATCH</t>
@@ -11722,7 +10528,7 @@
       <c r="D19" t="n">
         <v>68901</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -11758,7 +10564,7 @@
       <c r="D20" t="n">
         <v>68818</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
@@ -11792,7 +10598,7 @@
       <c r="D21" t="n">
         <v>68927</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
@@ -11826,7 +10632,7 @@
       <c r="D22" t="n">
         <v>68937</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
@@ -11860,7 +10666,7 @@
       <c r="D23" t="n">
         <v>68927</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
@@ -11894,7 +10700,7 @@
       <c r="D24" t="n">
         <v>68325</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
@@ -11928,6 +10734,7 @@
       <c r="D25" t="n">
         <v>68943</v>
       </c>
+      <c r="E25" s="6" t="n"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>NO MATCH</t>
@@ -11956,7 +10763,7 @@
       <c r="D26" t="n">
         <v>68326</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="6" t="n">
         <v>170</v>
       </c>
       <c r="F26" t="n">
@@ -11990,6 +10797,7 @@
       <c r="D27" t="n">
         <v>68827</v>
       </c>
+      <c r="E27" s="6" t="n"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>NO MATCH</t>
@@ -12018,7 +10826,7 @@
       <c r="D28" t="n">
         <v>68826</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
@@ -12052,6 +10860,7 @@
       <c r="D29" t="n">
         <v>68826</v>
       </c>
+      <c r="E29" s="6" t="n"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>NO CODE-CITY</t>
@@ -12080,6 +10889,7 @@
       <c r="D30" t="n">
         <v>68933</v>
       </c>
+      <c r="E30" s="6" t="n"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>NO CODE-CITY</t>
@@ -12108,6 +10918,7 @@
       <c r="D31" t="n">
         <v>68933</v>
       </c>
+      <c r="E31" s="6" t="n"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>NO CODE-CITY</t>
@@ -12136,7 +10947,7 @@
       <c r="D32" t="n">
         <v>68933</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="6" t="n">
         <v>94</v>
       </c>
       <c r="F32" t="n">
@@ -12170,7 +10981,7 @@
       <c r="D33" t="n">
         <v>68628</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="6" t="n">
         <v>94</v>
       </c>
       <c r="F33" t="n">
@@ -12204,7 +11015,7 @@
       <c r="D34" t="n">
         <v>69140</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="6" t="n">
         <v>104</v>
       </c>
       <c r="F34" t="n">
@@ -12238,7 +11049,7 @@
       <c r="D35" t="n">
         <v>68831</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="6" t="n">
         <v>104</v>
       </c>
       <c r="F35" t="n">
@@ -12272,7 +11083,7 @@
       <c r="D36" t="n">
         <v>68873</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="6" t="n">
         <v>104</v>
       </c>
       <c r="F36" t="n">
@@ -12306,7 +11117,7 @@
       <c r="D37" t="n">
         <v>68831</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
@@ -12340,7 +11151,7 @@
       <c r="D38" t="n">
         <v>68832</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
@@ -12374,7 +11185,7 @@
       <c r="D39" t="n">
         <v>68632</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="6" t="n">
         <v>134</v>
       </c>
       <c r="F39" t="n">
@@ -12408,7 +11219,7 @@
       <c r="D40" t="n">
         <v>68352</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
@@ -12442,7 +11253,7 @@
       <c r="D41" t="n">
         <v>68361</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="6" t="n">
         <v>134</v>
       </c>
       <c r="F41" t="n">
@@ -12476,7 +11287,7 @@
       <c r="D42" t="n">
         <v>68801</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="inlineStr">
@@ -12512,6 +11323,7 @@
       <c r="D43" t="n">
         <v>68801</v>
       </c>
+      <c r="E43" s="6" t="n"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>NO MATCH</t>
@@ -12540,7 +11352,7 @@
       <c r="D44" t="n">
         <v>68803</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
@@ -12574,7 +11386,7 @@
       <c r="D45" t="n">
         <v>68818</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
@@ -12608,7 +11420,7 @@
       <c r="D46" t="n">
         <v>68801</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
@@ -12642,7 +11454,7 @@
       <c r="D47" t="n">
         <v>68801</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
@@ -12676,7 +11488,7 @@
       <c r="D48" t="n">
         <v>68801</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
@@ -12710,7 +11522,7 @@
       <c r="D49" t="n">
         <v>68801</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
@@ -12744,7 +11556,7 @@
       <c r="D50" t="n">
         <v>68943</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
@@ -12778,7 +11590,7 @@
       <c r="D51" t="n">
         <v>68943</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
@@ -12812,7 +11624,7 @@
       <c r="D52" t="n">
         <v>68944</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
@@ -12846,7 +11658,7 @@
       <c r="D53" t="n">
         <v>68371</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
@@ -12880,7 +11692,7 @@
       <c r="D54" t="n">
         <v>68375</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
@@ -12914,7 +11726,7 @@
       <c r="D55" t="n">
         <v>68847</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
@@ -12948,7 +11760,7 @@
       <c r="D56" t="n">
         <v>68847</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
@@ -12982,7 +11794,7 @@
       <c r="D57" t="n">
         <v>68847</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
@@ -13016,7 +11828,7 @@
       <c r="D58" t="n">
         <v>68847</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
@@ -13050,7 +11862,7 @@
       <c r="D59" t="n">
         <v>68840</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
@@ -13084,7 +11896,7 @@
       <c r="D60" t="n">
         <v>68840</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
@@ -13118,7 +11930,7 @@
       <c r="D61" t="n">
         <v>68924</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
@@ -13152,7 +11964,7 @@
       <c r="D62" t="n">
         <v>68504</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
@@ -13186,7 +11998,7 @@
       <c r="D63" t="n">
         <v>68854</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
@@ -13220,7 +12032,7 @@
       <c r="D64" t="n">
         <v>68959</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
@@ -13254,7 +12066,7 @@
       <c r="D65" t="n">
         <v>68939</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
@@ -13288,7 +12100,7 @@
       <c r="D66" t="n">
         <v>68865</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
@@ -13322,7 +12134,7 @@
       <c r="D67" t="n">
         <v>68756</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
@@ -13356,7 +12168,7 @@
       <c r="D68" t="n">
         <v>68452</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
@@ -13390,7 +12202,7 @@
       <c r="D69" t="n">
         <v>68826</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="n">
@@ -13424,7 +12236,7 @@
       <c r="D70" t="n">
         <v>68847</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F70" t="n">
@@ -13458,7 +12270,7 @@
       <c r="D71" t="n">
         <v>68869</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F71" t="n">
@@ -13492,7 +12304,7 @@
       <c r="D72" t="n">
         <v>68873</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="inlineStr">
@@ -13528,7 +12340,7 @@
       <c r="D73" t="n">
         <v>68873</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
@@ -13562,7 +12374,7 @@
       <c r="D74" t="n">
         <v>68978</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F74" t="n">
@@ -13596,7 +12408,7 @@
       <c r="D75" t="n">
         <v>68978</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F75" t="n">
@@ -13630,7 +12442,7 @@
       <c r="D76" t="n">
         <v>68981</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F76" t="n">
@@ -13664,7 +12476,7 @@
       <c r="D77" t="n">
         <v>68981</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
@@ -13698,7 +12510,7 @@
       <c r="D78" t="n">
         <v>68883</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
@@ -13732,7 +12544,7 @@
       <c r="D79" t="n">
         <v>68467</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
@@ -13766,7 +12578,7 @@
       <c r="D80" t="n">
         <v>68467</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="inlineStr">
@@ -13802,7 +12614,7 @@
       <c r="D81" t="n">
         <v>68467</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F81" t="inlineStr">
@@ -13838,7 +12650,7 @@
       <c r="D82" t="n">
         <v>68818</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="inlineStr">
@@ -13874,6 +12686,7 @@
       <c r="D83" t="n">
         <v>68818</v>
       </c>
+      <c r="E83" s="6" t="n"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>NO MATCH</t>
@@ -13902,6 +12715,7 @@
       <c r="D84" t="n">
         <v>68371</v>
       </c>
+      <c r="E84" s="6" t="n"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>NO MATCH</t>
@@ -13930,7 +12744,7 @@
       <c r="D85" t="n">
         <v>68818</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="inlineStr">
@@ -13966,7 +12780,7 @@
       <c r="D86" t="n">
         <v>68818</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
@@ -14000,7 +12814,7 @@
       <c r="D87" t="n">
         <v>68818</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
@@ -14034,7 +12848,7 @@
       <c r="D88" t="n">
         <v>68848</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
@@ -14068,7 +12882,7 @@
       <c r="D89" t="n">
         <v>69140</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
@@ -14102,7 +12916,7 @@
       <c r="D90" t="n">
         <v>68701</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F90" t="n">
@@ -14136,6 +12950,7 @@
       <c r="D91" t="n">
         <v>68959</v>
       </c>
+      <c r="E91" s="6" t="n"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>NO MATCH</t>
@@ -14164,7 +12979,7 @@
       <c r="D92" t="n">
         <v>68818</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92" s="6" t="n">
         <v>170</v>
       </c>
       <c r="F92" t="n">
@@ -14198,7 +13013,7 @@
       <c r="D93" t="n">
         <v>68818</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
@@ -14232,7 +13047,7 @@
       <c r="D94" t="n">
         <v>68818</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F94" t="n">
